--- a/02_crm_transactions.xlsx
+++ b/02_crm_transactions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="65">
   <si>
     <t>transaction_id</t>
   </si>
@@ -131,6 +131,81 @@
   </si>
   <si>
     <t>P099</t>
+  </si>
+  <si>
+    <t>D019</t>
+  </si>
+  <si>
+    <t>D020</t>
+  </si>
+  <si>
+    <t>D021</t>
+  </si>
+  <si>
+    <t>D022</t>
+  </si>
+  <si>
+    <t>D023</t>
+  </si>
+  <si>
+    <t>D024</t>
+  </si>
+  <si>
+    <t>P006</t>
+  </si>
+  <si>
+    <t>D025</t>
+  </si>
+  <si>
+    <t>D026</t>
+  </si>
+  <si>
+    <t>D027</t>
+  </si>
+  <si>
+    <t>D028</t>
+  </si>
+  <si>
+    <t>D029</t>
+  </si>
+  <si>
+    <t>D030</t>
+  </si>
+  <si>
+    <t>D031</t>
+  </si>
+  <si>
+    <t>D032</t>
+  </si>
+  <si>
+    <t>D033</t>
+  </si>
+  <si>
+    <t>D034</t>
+  </si>
+  <si>
+    <t>D035</t>
+  </si>
+  <si>
+    <t>D036</t>
+  </si>
+  <si>
+    <t>D037</t>
+  </si>
+  <si>
+    <t>D038</t>
+  </si>
+  <si>
+    <t>D039</t>
+  </si>
+  <si>
+    <t>D040</t>
+  </si>
+  <si>
+    <t>D041</t>
+  </si>
+  <si>
+    <t>D042</t>
   </si>
 </sst>
 </file>
@@ -393,6 +468,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="8.13"/>
+    <col customWidth="1" min="3" max="3" width="22.88"/>
+    <col customWidth="1" min="4" max="4" width="15.63"/>
+    <col customWidth="1" min="5" max="5" width="18.38"/>
+    <col customWidth="1" min="6" max="6" width="32.38"/>
+    <col customWidth="1" min="8" max="8" width="51.0"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -1002,6 +1085,792 @@
         <v>100.0</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1017.0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>45679.0</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>40000.0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>200000.0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1018.0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>45693.0</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>25000.0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>75000.0</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1019.0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>45706.0</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="F22" s="1">
+        <v>15000.0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>60000.0</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J22" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1020.0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>45710.0</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F23" s="1">
+        <v>40000.0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>240000.0</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1021.0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>45713.0</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="F24" s="1">
+        <v>25000.0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>125000.0</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1022.0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>45717.0</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F25" s="1">
+        <v>22000.0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>66000.0</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J25" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1023.0</v>
+      </c>
+      <c r="C26" s="2">
+        <v>45721.0</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="F26" s="1">
+        <v>15000.0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>120000.0</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1024.0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>45724.0</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="F27" s="1">
+        <v>40000.0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>160000.0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1025.0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>45726.0</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F28" s="1">
+        <v>25000.0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>150000.0</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J28" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1026.0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>45728.0</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F29" s="1">
+        <v>22000.0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>44000.0</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1027.0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>45731.0</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="F30" s="1">
+        <v>15000.0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>75000.0</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="1">
+        <v>1028.0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>45734.0</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F31" s="1">
+        <v>40000.0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>280000.0</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1029.0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>45736.0</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="F32" s="1">
+        <v>25000.0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>100000.0</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="1">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1030.0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>45738.0</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F33" s="1">
+        <v>15000.0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>45000.0</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="1">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1031.0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>45739.0</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="F34" s="1">
+        <v>40000.0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>200000.0</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J34" s="1">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1032.0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>45740.0</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F35" s="1">
+        <v>25000.0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>50000.0</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1033.0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>45741.0</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="F36" s="1">
+        <v>22000.0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>88000.0</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1034.0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>45742.0</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F37" s="1">
+        <v>15000.0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>90000.0</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J37" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1035.0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>45743.0</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="F38" s="1">
+        <v>40000.0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>320000.0</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="1">
+        <v>1036.0</v>
+      </c>
+      <c r="C39" s="2">
+        <v>45744.0</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="F39" s="1">
+        <v>25000.0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>125000.0</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="1">
+        <v>1037.0</v>
+      </c>
+      <c r="C40" s="2">
+        <v>45745.0</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F40" s="1">
+        <v>22000.0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>66000.0</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J40" s="1">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1038.0</v>
+      </c>
+      <c r="C41" s="2">
+        <v>45746.0</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="F41" s="1">
+        <v>15000.0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>60000.0</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="1">
+        <v>1039.0</v>
+      </c>
+      <c r="C42" s="2">
+        <v>45747.0</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="F42" s="1">
+        <v>40000.0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>240000.0</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" s="1">
+        <v>1040.0</v>
+      </c>
+      <c r="C43" s="2">
+        <v>45747.0</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F43" s="1">
+        <v>25000.0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>75000.0</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J43" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
